--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>57.70873080096981</v>
+        <v>9.377668755157595</v>
       </c>
       <c r="D2" t="n">
-        <v>57.60490278267641</v>
+        <v>9.360796702184917</v>
       </c>
       <c r="E2" t="n">
-        <v>14.8932355891702</v>
+        <v>2.420150783240159</v>
       </c>
       <c r="F2" t="n">
-        <v>14.71674525505282</v>
+        <v>2.391471103946083</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.56288235355147</v>
+        <v>7.728968382452114</v>
       </c>
       <c r="D3" t="n">
-        <v>45.77610063001094</v>
+        <v>7.438616352376779</v>
       </c>
       <c r="E3" t="n">
-        <v>14.8932355891702</v>
+        <v>2.420150783240159</v>
       </c>
       <c r="F3" t="n">
-        <v>14.71674525505282</v>
+        <v>2.391471103946083</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.53230425841211</v>
+        <v>4.473999441991968</v>
       </c>
       <c r="D4" t="n">
-        <v>26.02149218541388</v>
+        <v>4.228492480129755</v>
       </c>
       <c r="E4" t="n">
-        <v>14.8932355891702</v>
+        <v>2.420150783240159</v>
       </c>
       <c r="F4" t="n">
-        <v>14.71674525505282</v>
+        <v>2.391471103946083</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.25139318659556</v>
+        <v>2.803351392821778</v>
       </c>
       <c r="D5" t="n">
-        <v>16.83058676707677</v>
+        <v>2.734970349649975</v>
       </c>
       <c r="E5" t="n">
-        <v>14.8932355891702</v>
+        <v>2.420150783240159</v>
       </c>
       <c r="F5" t="n">
-        <v>14.71674525505282</v>
+        <v>2.391471103946083</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.90559627867614</v>
+        <v>4.372159395284872</v>
       </c>
       <c r="D6" t="n">
-        <v>28.28341190324974</v>
+        <v>4.596054434278083</v>
       </c>
       <c r="E6" t="n">
-        <v>14.8932355891702</v>
+        <v>2.420150783240159</v>
       </c>
       <c r="F6" t="n">
-        <v>14.71674525505282</v>
+        <v>2.391471103946083</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
